--- a/docs/downloads/04/tbl_other_act_all_alaotra_analamiranga.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_analamiranga.xlsx
@@ -387,12 +387,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +411,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +423,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +435,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -513,12 +483,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +495,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +507,6 @@
           <t>Inactif, Chômeur ? Tsy miasa, tsy an?asa</t>
         </is>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -616,12 +568,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +580,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +592,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +604,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +616,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +628,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +640,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -760,12 +670,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,12 +682,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -796,12 +694,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -832,12 +724,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -886,12 +772,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -922,12 +802,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -940,12 +814,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -976,12 +844,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -994,12 +856,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1048,12 +904,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1084,12 +934,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1138,12 +982,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1156,12 +994,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1174,12 +1006,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
-      <c r="D46">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1192,12 +1018,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1227,12 +1047,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
       </c>
     </row>
     <row r="50">
